--- a/Train Automation System/Grading/2 stage/6-examples/Train-Automation-System_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_GPT5.5AutoGrading.xlsx
+++ b/Train Automation System/Grading/2 stage/6-examples/Train-Automation-System_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_GPT5.5AutoGrading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19780" yWindow="-21000" windowWidth="30240" windowHeight="17300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Train Automation System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini Generation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Train Automation System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GPT-5.5 Grading" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1158,11 +1158,11 @@
     </row>
     <row r="2" ht="12.75" customHeight="1" s="69">
       <c r="A2" s="4">
-        <f>'GPT-5 Generation'!A2</f>
+        <f>'GPT-5.5 Grading'!A2</f>
         <v/>
       </c>
       <c r="B2" s="4">
-        <f>'GPT-5 Generation'!B2</f>
+        <f>'GPT-5.5 Grading'!B2</f>
         <v/>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -1170,11 +1170,11 @@
     </row>
     <row r="3" ht="12.75" customHeight="1" s="69">
       <c r="A3" s="4">
-        <f>'GPT-5 Generation'!A3</f>
+        <f>'GPT-5.5 Grading'!A3</f>
         <v/>
       </c>
       <c r="B3" s="4">
-        <f>'GPT-5 Generation'!B3</f>
+        <f>'GPT-5.5 Grading'!B3</f>
         <v/>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -1182,11 +1182,11 @@
     </row>
     <row r="4" ht="12.75" customHeight="1" s="69">
       <c r="A4" s="4">
-        <f>'GPT-5 Generation'!A4</f>
+        <f>'GPT-5.5 Grading'!A4</f>
         <v/>
       </c>
       <c r="B4" s="4">
-        <f>'GPT-5 Generation'!B4</f>
+        <f>'GPT-5.5 Grading'!B4</f>
         <v/>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -1194,11 +1194,11 @@
     </row>
     <row r="5" ht="12.75" customHeight="1" s="69">
       <c r="A5" s="4">
-        <f>'GPT-5 Generation'!A5</f>
+        <f>'GPT-5.5 Grading'!A5</f>
         <v/>
       </c>
       <c r="B5" s="4">
-        <f>'GPT-5 Generation'!B5</f>
+        <f>'GPT-5.5 Grading'!B5</f>
         <v/>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -1206,11 +1206,11 @@
     </row>
     <row r="6" ht="12.75" customHeight="1" s="69">
       <c r="A6" s="4">
-        <f>'GPT-5 Generation'!A6</f>
+        <f>'GPT-5.5 Grading'!A6</f>
         <v/>
       </c>
       <c r="B6" s="4">
-        <f>'GPT-5 Generation'!B6</f>
+        <f>'GPT-5.5 Grading'!B6</f>
         <v/>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -1218,11 +1218,11 @@
     </row>
     <row r="7" ht="12.75" customHeight="1" s="69">
       <c r="A7" s="4">
-        <f>'GPT-5 Generation'!A7</f>
+        <f>'GPT-5.5 Grading'!A7</f>
         <v/>
       </c>
       <c r="B7" s="4">
-        <f>'GPT-5 Generation'!B7</f>
+        <f>'GPT-5.5 Grading'!B7</f>
         <v/>
       </c>
       <c r="C7" s="5" t="n"/>
@@ -1230,11 +1230,11 @@
     </row>
     <row r="8" ht="12.75" customHeight="1" s="69">
       <c r="A8" s="4">
-        <f>'GPT-5 Generation'!A8</f>
+        <f>'GPT-5.5 Grading'!A8</f>
         <v/>
       </c>
       <c r="B8" s="4">
-        <f>'GPT-5 Generation'!B8</f>
+        <f>'GPT-5.5 Grading'!B8</f>
         <v/>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -1242,11 +1242,11 @@
     </row>
     <row r="9" ht="12.75" customHeight="1" s="69">
       <c r="A9" s="4">
-        <f>'GPT-5 Generation'!A9</f>
+        <f>'GPT-5.5 Grading'!A9</f>
         <v/>
       </c>
       <c r="B9" s="4">
-        <f>'GPT-5 Generation'!B9</f>
+        <f>'GPT-5.5 Grading'!B9</f>
         <v/>
       </c>
       <c r="C9" s="5" t="n"/>
@@ -1254,11 +1254,11 @@
     </row>
     <row r="10" ht="12.75" customHeight="1" s="69">
       <c r="A10" s="4">
-        <f>'GPT-5 Generation'!A10</f>
+        <f>'GPT-5.5 Grading'!A10</f>
         <v/>
       </c>
       <c r="B10" s="4">
-        <f>'GPT-5 Generation'!B10</f>
+        <f>'GPT-5.5 Grading'!B10</f>
         <v/>
       </c>
       <c r="C10" s="5" t="n"/>
@@ -1266,11 +1266,11 @@
     </row>
     <row r="11" ht="12.75" customHeight="1" s="69">
       <c r="A11" s="4">
-        <f>'GPT-5 Generation'!A11</f>
+        <f>'GPT-5.5 Grading'!A11</f>
         <v/>
       </c>
       <c r="B11" s="4">
-        <f>'GPT-5 Generation'!B11</f>
+        <f>'GPT-5.5 Grading'!B11</f>
         <v/>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -1278,11 +1278,11 @@
     </row>
     <row r="12" ht="12.75" customHeight="1" s="69">
       <c r="A12" s="4">
-        <f>'GPT-5 Generation'!A12</f>
+        <f>'GPT-5.5 Grading'!A12</f>
         <v/>
       </c>
       <c r="B12" s="4">
-        <f>'GPT-5 Generation'!B12</f>
+        <f>'GPT-5.5 Grading'!B12</f>
         <v/>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -1290,11 +1290,11 @@
     </row>
     <row r="13" ht="12.75" customHeight="1" s="69">
       <c r="A13" s="4">
-        <f>'GPT-5 Generation'!A13</f>
+        <f>'GPT-5.5 Grading'!A13</f>
         <v/>
       </c>
       <c r="B13" s="4">
-        <f>'GPT-5 Generation'!B13</f>
+        <f>'GPT-5.5 Grading'!B13</f>
         <v/>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -1302,11 +1302,11 @@
     </row>
     <row r="14" ht="12.75" customHeight="1" s="69">
       <c r="A14" s="4">
-        <f>'GPT-5 Generation'!A14</f>
+        <f>'GPT-5.5 Grading'!A14</f>
         <v/>
       </c>
       <c r="B14" s="4">
-        <f>'GPT-5 Generation'!B14</f>
+        <f>'GPT-5.5 Grading'!B14</f>
         <v/>
       </c>
       <c r="C14" s="5" t="n"/>
@@ -1314,11 +1314,11 @@
     </row>
     <row r="15" ht="12.75" customHeight="1" s="69">
       <c r="A15" s="4">
-        <f>'GPT-5 Generation'!A15</f>
+        <f>'GPT-5.5 Grading'!A15</f>
         <v/>
       </c>
       <c r="B15" s="4">
-        <f>'GPT-5 Generation'!B15</f>
+        <f>'GPT-5.5 Grading'!B15</f>
         <v/>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -1326,11 +1326,11 @@
     </row>
     <row r="16" ht="12.75" customHeight="1" s="69">
       <c r="A16" s="4">
-        <f>'GPT-5 Generation'!A16</f>
+        <f>'GPT-5.5 Grading'!A16</f>
         <v/>
       </c>
       <c r="B16" s="4">
-        <f>'GPT-5 Generation'!B16</f>
+        <f>'GPT-5.5 Grading'!B16</f>
         <v/>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -1338,11 +1338,11 @@
     </row>
     <row r="17" ht="15" customHeight="1" s="69">
       <c r="A17" s="4">
-        <f>'GPT-5 Generation'!A17</f>
+        <f>'GPT-5.5 Grading'!A17</f>
         <v/>
       </c>
       <c r="B17" s="4">
-        <f>'GPT-5 Generation'!B17</f>
+        <f>'GPT-5.5 Grading'!B17</f>
         <v/>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -1368,11 +1368,11 @@
     </row>
     <row r="18" ht="12.75" customHeight="1" s="69">
       <c r="A18" s="4">
-        <f>'GPT-5 Generation'!A18</f>
+        <f>'GPT-5.5 Grading'!A18</f>
         <v/>
       </c>
       <c r="B18" s="4">
-        <f>'GPT-5 Generation'!B18</f>
+        <f>'GPT-5.5 Grading'!B18</f>
         <v/>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -1380,11 +1380,11 @@
     </row>
     <row r="19" ht="12.75" customHeight="1" s="69">
       <c r="A19" s="4">
-        <f>'GPT-5 Generation'!A19</f>
+        <f>'GPT-5.5 Grading'!A19</f>
         <v/>
       </c>
       <c r="B19" s="4">
-        <f>'GPT-5 Generation'!B19</f>
+        <f>'GPT-5.5 Grading'!B19</f>
         <v/>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -1392,11 +1392,11 @@
     </row>
     <row r="20" ht="12.75" customHeight="1" s="69">
       <c r="A20" s="4">
-        <f>'GPT-5 Generation'!A20</f>
+        <f>'GPT-5.5 Grading'!A20</f>
         <v/>
       </c>
       <c r="B20" s="4">
-        <f>'GPT-5 Generation'!B20</f>
+        <f>'GPT-5.5 Grading'!B20</f>
         <v/>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -1404,11 +1404,11 @@
     </row>
     <row r="21" ht="12.75" customHeight="1" s="69">
       <c r="A21" s="4">
-        <f>'GPT-5 Generation'!A21</f>
+        <f>'GPT-5.5 Grading'!A21</f>
         <v/>
       </c>
       <c r="B21" s="4">
-        <f>'GPT-5 Generation'!B21</f>
+        <f>'GPT-5.5 Grading'!B21</f>
         <v/>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -1416,11 +1416,11 @@
     </row>
     <row r="22" ht="12.75" customHeight="1" s="69">
       <c r="A22" s="4">
-        <f>'GPT-5 Generation'!A22</f>
+        <f>'GPT-5.5 Grading'!A22</f>
         <v/>
       </c>
       <c r="B22" s="4">
-        <f>'GPT-5 Generation'!B22</f>
+        <f>'GPT-5.5 Grading'!B22</f>
         <v/>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -1428,11 +1428,11 @@
     </row>
     <row r="23" ht="12.75" customHeight="1" s="69">
       <c r="A23" s="4">
-        <f>'GPT-5 Generation'!A23</f>
+        <f>'GPT-5.5 Grading'!A23</f>
         <v/>
       </c>
       <c r="B23" s="4">
-        <f>'GPT-5 Generation'!B23</f>
+        <f>'GPT-5.5 Grading'!B23</f>
         <v/>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -1458,11 +1458,11 @@
     </row>
     <row r="24" ht="12.75" customHeight="1" s="69">
       <c r="A24" s="4">
-        <f>'GPT-5 Generation'!A24</f>
+        <f>'GPT-5.5 Grading'!A24</f>
         <v/>
       </c>
       <c r="B24" s="4">
-        <f>'GPT-5 Generation'!B24</f>
+        <f>'GPT-5.5 Grading'!B24</f>
         <v/>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -1470,11 +1470,11 @@
     </row>
     <row r="25" ht="12.75" customHeight="1" s="69">
       <c r="A25" s="4">
-        <f>'GPT-5 Generation'!A25</f>
+        <f>'GPT-5.5 Grading'!A25</f>
         <v/>
       </c>
       <c r="B25" s="4">
-        <f>'GPT-5 Generation'!B25</f>
+        <f>'GPT-5.5 Grading'!B25</f>
         <v/>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -1482,11 +1482,11 @@
     </row>
     <row r="26" ht="15" customHeight="1" s="69">
       <c r="A26" s="4">
-        <f>'GPT-5 Generation'!A26</f>
+        <f>'GPT-5.5 Grading'!A26</f>
         <v/>
       </c>
       <c r="B26" s="4">
-        <f>'GPT-5 Generation'!B26</f>
+        <f>'GPT-5.5 Grading'!B26</f>
         <v/>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -1494,11 +1494,11 @@
     </row>
     <row r="27" ht="12.75" customHeight="1" s="69">
       <c r="A27" s="4">
-        <f>'GPT-5 Generation'!A27</f>
+        <f>'GPT-5.5 Grading'!A27</f>
         <v/>
       </c>
       <c r="B27" s="4">
-        <f>'GPT-5 Generation'!B27</f>
+        <f>'GPT-5.5 Grading'!B27</f>
         <v/>
       </c>
       <c r="C27" s="5" t="n"/>
@@ -1506,11 +1506,11 @@
     </row>
     <row r="28" ht="12.75" customHeight="1" s="69">
       <c r="A28" s="4">
-        <f>'GPT-5 Generation'!A28</f>
+        <f>'GPT-5.5 Grading'!A28</f>
         <v/>
       </c>
       <c r="B28" s="4">
-        <f>'GPT-5 Generation'!B28</f>
+        <f>'GPT-5.5 Grading'!B28</f>
         <v/>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -1518,11 +1518,11 @@
     </row>
     <row r="29" ht="12.75" customHeight="1" s="69">
       <c r="A29" s="4">
-        <f>'GPT-5 Generation'!A29</f>
+        <f>'GPT-5.5 Grading'!A29</f>
         <v/>
       </c>
       <c r="B29" s="4">
-        <f>'GPT-5 Generation'!B29</f>
+        <f>'GPT-5.5 Grading'!B29</f>
         <v/>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -1530,11 +1530,11 @@
     </row>
     <row r="30" ht="12.75" customHeight="1" s="69">
       <c r="A30" s="4">
-        <f>'GPT-5 Generation'!A30</f>
+        <f>'GPT-5.5 Grading'!A30</f>
         <v/>
       </c>
       <c r="B30" s="4">
-        <f>'GPT-5 Generation'!B30</f>
+        <f>'GPT-5.5 Grading'!B30</f>
         <v/>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -1560,11 +1560,11 @@
     </row>
     <row r="31" ht="12.75" customHeight="1" s="69">
       <c r="A31" s="4">
-        <f>'GPT-5 Generation'!A31</f>
+        <f>'GPT-5.5 Grading'!A31</f>
         <v/>
       </c>
       <c r="B31" s="4">
-        <f>'GPT-5 Generation'!B31</f>
+        <f>'GPT-5.5 Grading'!B31</f>
         <v/>
       </c>
       <c r="C31" s="5" t="n"/>
@@ -1590,11 +1590,11 @@
     </row>
     <row r="32" ht="12.75" customHeight="1" s="69">
       <c r="A32" s="4">
-        <f>'GPT-5 Generation'!A32</f>
+        <f>'GPT-5.5 Grading'!A32</f>
         <v/>
       </c>
       <c r="B32" s="4">
-        <f>'GPT-5 Generation'!B32</f>
+        <f>'GPT-5.5 Grading'!B32</f>
         <v/>
       </c>
       <c r="C32" s="5" t="n"/>
@@ -1602,11 +1602,11 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" s="69">
       <c r="A33" s="4">
-        <f>'GPT-5 Generation'!A33</f>
+        <f>'GPT-5.5 Grading'!A33</f>
         <v/>
       </c>
       <c r="B33" s="4">
-        <f>'GPT-5 Generation'!B33</f>
+        <f>'GPT-5.5 Grading'!B33</f>
         <v/>
       </c>
       <c r="C33" s="5" t="n"/>
@@ -1614,11 +1614,11 @@
     </row>
     <row r="34" ht="12.75" customHeight="1" s="69">
       <c r="A34" s="4">
-        <f>'GPT-5 Generation'!A34</f>
+        <f>'GPT-5.5 Grading'!A34</f>
         <v/>
       </c>
       <c r="B34" s="4">
-        <f>'GPT-5 Generation'!B34</f>
+        <f>'GPT-5.5 Grading'!B34</f>
         <v/>
       </c>
       <c r="C34" s="5" t="n"/>
@@ -1626,11 +1626,11 @@
     </row>
     <row r="35" ht="12.75" customHeight="1" s="69">
       <c r="A35" s="4">
-        <f>'GPT-5 Generation'!A35</f>
+        <f>'GPT-5.5 Grading'!A35</f>
         <v/>
       </c>
       <c r="B35" s="4">
-        <f>'GPT-5 Generation'!B35</f>
+        <f>'GPT-5.5 Grading'!B35</f>
         <v/>
       </c>
       <c r="C35" s="5" t="n"/>
@@ -1638,11 +1638,11 @@
     </row>
     <row r="36" ht="12.75" customHeight="1" s="69">
       <c r="A36" s="4">
-        <f>'GPT-5 Generation'!A36</f>
+        <f>'GPT-5.5 Grading'!A36</f>
         <v/>
       </c>
       <c r="B36" s="4">
-        <f>'GPT-5 Generation'!B36</f>
+        <f>'GPT-5.5 Grading'!B36</f>
         <v/>
       </c>
       <c r="C36" s="5" t="n"/>
@@ -1650,11 +1650,11 @@
     </row>
     <row r="37" ht="12.75" customHeight="1" s="69">
       <c r="A37" s="4">
-        <f>'GPT-5 Generation'!A37</f>
+        <f>'GPT-5.5 Grading'!A37</f>
         <v/>
       </c>
       <c r="B37" s="4">
-        <f>'GPT-5 Generation'!B37</f>
+        <f>'GPT-5.5 Grading'!B37</f>
         <v/>
       </c>
       <c r="C37" s="5" t="n"/>
@@ -1662,11 +1662,11 @@
     </row>
     <row r="38" ht="15" customHeight="1" s="69">
       <c r="A38" s="4">
-        <f>'GPT-5 Generation'!A38</f>
+        <f>'GPT-5.5 Grading'!A38</f>
         <v/>
       </c>
       <c r="B38" s="4">
-        <f>'GPT-5 Generation'!B38</f>
+        <f>'GPT-5.5 Grading'!B38</f>
         <v/>
       </c>
       <c r="C38" s="5" t="n"/>
@@ -1692,11 +1692,11 @@
     </row>
     <row r="39" ht="15" customHeight="1" s="69">
       <c r="A39" s="4">
-        <f>'GPT-5 Generation'!A39</f>
+        <f>'GPT-5.5 Grading'!A39</f>
         <v/>
       </c>
       <c r="B39" s="4">
-        <f>'GPT-5 Generation'!B39</f>
+        <f>'GPT-5.5 Grading'!B39</f>
         <v/>
       </c>
       <c r="C39" s="5" t="n"/>
@@ -1722,11 +1722,11 @@
     </row>
     <row r="40" ht="15" customHeight="1" s="69">
       <c r="A40" s="4">
-        <f>'GPT-5 Generation'!A40</f>
+        <f>'GPT-5.5 Grading'!A40</f>
         <v/>
       </c>
       <c r="B40" s="4">
-        <f>'GPT-5 Generation'!B40</f>
+        <f>'GPT-5.5 Grading'!B40</f>
         <v/>
       </c>
       <c r="C40" s="5" t="n"/>
@@ -1752,11 +1752,11 @@
     </row>
     <row r="41" ht="15" customHeight="1" s="69">
       <c r="A41" s="4">
-        <f>'GPT-5 Generation'!A41</f>
+        <f>'GPT-5.5 Grading'!A41</f>
         <v/>
       </c>
       <c r="B41" s="4">
-        <f>'GPT-5 Generation'!B41</f>
+        <f>'GPT-5.5 Grading'!B41</f>
         <v/>
       </c>
       <c r="C41" s="5" t="n"/>
@@ -1782,11 +1782,11 @@
     </row>
     <row r="42" ht="15" customHeight="1" s="69">
       <c r="A42" s="4">
-        <f>'GPT-5 Generation'!A42</f>
+        <f>'GPT-5.5 Grading'!A42</f>
         <v/>
       </c>
       <c r="B42" s="4">
-        <f>'GPT-5 Generation'!B42</f>
+        <f>'GPT-5.5 Grading'!B42</f>
         <v/>
       </c>
       <c r="C42" s="5" t="n"/>
@@ -1812,11 +1812,11 @@
     </row>
     <row r="43" ht="15" customHeight="1" s="69">
       <c r="A43" s="4">
-        <f>'GPT-5 Generation'!A43</f>
+        <f>'GPT-5.5 Grading'!A43</f>
         <v/>
       </c>
       <c r="B43" s="4">
-        <f>'GPT-5 Generation'!B43</f>
+        <f>'GPT-5.5 Grading'!B43</f>
         <v/>
       </c>
       <c r="C43" s="5" t="n"/>
@@ -1842,11 +1842,11 @@
     </row>
     <row r="44" ht="15" customHeight="1" s="69">
       <c r="A44" s="4">
-        <f>'GPT-5 Generation'!A44</f>
+        <f>'GPT-5.5 Grading'!A44</f>
         <v/>
       </c>
       <c r="B44" s="4">
-        <f>'GPT-5 Generation'!B44</f>
+        <f>'GPT-5.5 Grading'!B44</f>
         <v/>
       </c>
       <c r="C44" s="5" t="n"/>
@@ -1872,11 +1872,11 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="69">
       <c r="A45" s="4">
-        <f>'GPT-5 Generation'!A45</f>
+        <f>'GPT-5.5 Grading'!A45</f>
         <v/>
       </c>
       <c r="B45" s="4">
-        <f>'GPT-5 Generation'!B45</f>
+        <f>'GPT-5.5 Grading'!B45</f>
         <v/>
       </c>
       <c r="C45" s="5" t="n"/>
@@ -1902,11 +1902,11 @@
     </row>
     <row r="46" ht="15" customHeight="1" s="69">
       <c r="A46" s="4">
-        <f>'GPT-5 Generation'!A46</f>
+        <f>'GPT-5.5 Grading'!A46</f>
         <v/>
       </c>
       <c r="B46" s="4">
-        <f>'GPT-5 Generation'!B46</f>
+        <f>'GPT-5.5 Grading'!B46</f>
         <v/>
       </c>
       <c r="C46" s="5" t="n"/>
@@ -1932,11 +1932,11 @@
     </row>
     <row r="47" ht="15" customHeight="1" s="69">
       <c r="A47" s="4">
-        <f>'GPT-5 Generation'!A47</f>
+        <f>'GPT-5.5 Grading'!A47</f>
         <v/>
       </c>
       <c r="B47" s="4">
-        <f>'GPT-5 Generation'!B47</f>
+        <f>'GPT-5.5 Grading'!B47</f>
         <v/>
       </c>
       <c r="C47" s="5" t="n"/>
@@ -1962,11 +1962,11 @@
     </row>
     <row r="48" ht="12.75" customHeight="1" s="69">
       <c r="A48" s="4">
-        <f>'GPT-5 Generation'!A48</f>
+        <f>'GPT-5.5 Grading'!A48</f>
         <v/>
       </c>
       <c r="B48" s="4">
-        <f>'GPT-5 Generation'!B48</f>
+        <f>'GPT-5.5 Grading'!B48</f>
         <v/>
       </c>
       <c r="C48" s="5" t="n"/>
@@ -1974,11 +1974,11 @@
     </row>
     <row r="49" ht="12.75" customHeight="1" s="69">
       <c r="A49" s="4">
-        <f>'GPT-5 Generation'!A49</f>
+        <f>'GPT-5.5 Grading'!A49</f>
         <v/>
       </c>
       <c r="B49" s="4">
-        <f>'GPT-5 Generation'!B49</f>
+        <f>'GPT-5.5 Grading'!B49</f>
         <v/>
       </c>
       <c r="C49" s="5" t="n"/>
@@ -1986,11 +1986,11 @@
     </row>
     <row r="50" ht="12.75" customHeight="1" s="69">
       <c r="A50" s="4">
-        <f>'GPT-5 Generation'!A50</f>
+        <f>'GPT-5.5 Grading'!A50</f>
         <v/>
       </c>
       <c r="B50" s="4">
-        <f>'GPT-5 Generation'!B50</f>
+        <f>'GPT-5.5 Grading'!B50</f>
         <v/>
       </c>
       <c r="C50" s="5" t="n"/>
@@ -1998,11 +1998,11 @@
     </row>
     <row r="51" ht="12.75" customHeight="1" s="69">
       <c r="A51" s="4">
-        <f>'GPT-5 Generation'!A51</f>
+        <f>'GPT-5.5 Grading'!A51</f>
         <v/>
       </c>
       <c r="B51" s="4">
-        <f>'GPT-5 Generation'!B51</f>
+        <f>'GPT-5.5 Grading'!B51</f>
         <v/>
       </c>
       <c r="C51" s="5" t="n"/>
@@ -2010,11 +2010,11 @@
     </row>
     <row r="52" ht="12.75" customHeight="1" s="69">
       <c r="A52" s="4">
-        <f>'GPT-5 Generation'!A52</f>
+        <f>'GPT-5.5 Grading'!A52</f>
         <v/>
       </c>
       <c r="B52" s="4">
-        <f>'GPT-5 Generation'!B52</f>
+        <f>'GPT-5.5 Grading'!B52</f>
         <v/>
       </c>
       <c r="C52" s="5" t="n"/>
@@ -2022,11 +2022,11 @@
     </row>
     <row r="53" ht="12.75" customHeight="1" s="69">
       <c r="A53" s="4">
-        <f>'GPT-5 Generation'!A53</f>
+        <f>'GPT-5.5 Grading'!A53</f>
         <v/>
       </c>
       <c r="B53" s="4">
-        <f>'GPT-5 Generation'!B53</f>
+        <f>'GPT-5.5 Grading'!B53</f>
         <v/>
       </c>
       <c r="C53" s="5" t="n"/>
@@ -2034,11 +2034,11 @@
     </row>
     <row r="54" ht="12.75" customHeight="1" s="69">
       <c r="A54" s="4">
-        <f>'GPT-5 Generation'!A54</f>
+        <f>'GPT-5.5 Grading'!A54</f>
         <v/>
       </c>
       <c r="B54" s="4">
-        <f>'GPT-5 Generation'!B54</f>
+        <f>'GPT-5.5 Grading'!B54</f>
         <v/>
       </c>
       <c r="C54" s="5" t="n"/>
@@ -2046,11 +2046,11 @@
     </row>
     <row r="55" ht="12.75" customHeight="1" s="69">
       <c r="A55" s="4">
-        <f>'GPT-5 Generation'!A55</f>
+        <f>'GPT-5.5 Grading'!A55</f>
         <v/>
       </c>
       <c r="B55" s="4">
-        <f>'GPT-5 Generation'!B55</f>
+        <f>'GPT-5.5 Grading'!B55</f>
         <v/>
       </c>
       <c r="C55" s="5" t="n"/>
@@ -2058,11 +2058,11 @@
     </row>
     <row r="56" ht="12.75" customHeight="1" s="69">
       <c r="A56" s="4">
-        <f>'GPT-5 Generation'!A56</f>
+        <f>'GPT-5.5 Grading'!A56</f>
         <v/>
       </c>
       <c r="B56" s="4">
-        <f>'GPT-5 Generation'!B56</f>
+        <f>'GPT-5.5 Grading'!B56</f>
         <v/>
       </c>
       <c r="C56" s="5" t="n"/>
@@ -2070,11 +2070,11 @@
     </row>
     <row r="57" ht="12.75" customHeight="1" s="69">
       <c r="A57" s="4">
-        <f>'GPT-5 Generation'!A57</f>
+        <f>'GPT-5.5 Grading'!A57</f>
         <v/>
       </c>
       <c r="B57" s="4">
-        <f>'GPT-5 Generation'!B57</f>
+        <f>'GPT-5.5 Grading'!B57</f>
         <v/>
       </c>
       <c r="C57" s="5" t="n"/>
@@ -2082,11 +2082,11 @@
     </row>
     <row r="58" ht="12.75" customHeight="1" s="69">
       <c r="A58" s="4">
-        <f>'GPT-5 Generation'!A58</f>
+        <f>'GPT-5.5 Grading'!A58</f>
         <v/>
       </c>
       <c r="B58" s="4">
-        <f>'GPT-5 Generation'!B58</f>
+        <f>'GPT-5.5 Grading'!B58</f>
         <v/>
       </c>
       <c r="C58" s="5" t="n"/>
@@ -2094,11 +2094,11 @@
     </row>
     <row r="59" ht="12.75" customHeight="1" s="69">
       <c r="A59" s="4">
-        <f>'GPT-5 Generation'!A59</f>
+        <f>'GPT-5.5 Grading'!A59</f>
         <v/>
       </c>
       <c r="B59" s="4">
-        <f>'GPT-5 Generation'!B59</f>
+        <f>'GPT-5.5 Grading'!B59</f>
         <v/>
       </c>
       <c r="C59" s="5" t="n"/>
@@ -2106,11 +2106,11 @@
     </row>
     <row r="60" ht="12.75" customHeight="1" s="69">
       <c r="A60" s="4">
-        <f>'GPT-5 Generation'!A60</f>
+        <f>'GPT-5.5 Grading'!A60</f>
         <v/>
       </c>
       <c r="B60" s="4">
-        <f>'GPT-5 Generation'!B60</f>
+        <f>'GPT-5.5 Grading'!B60</f>
         <v/>
       </c>
       <c r="C60" s="5" t="n"/>
@@ -2118,11 +2118,11 @@
     </row>
     <row r="61" ht="12.75" customHeight="1" s="69">
       <c r="A61" s="4">
-        <f>'GPT-5 Generation'!A61</f>
+        <f>'GPT-5.5 Grading'!A61</f>
         <v/>
       </c>
       <c r="B61" s="4">
-        <f>'GPT-5 Generation'!B61</f>
+        <f>'GPT-5.5 Grading'!B61</f>
         <v/>
       </c>
       <c r="C61" s="5" t="n"/>
@@ -2130,11 +2130,11 @@
     </row>
     <row r="62" ht="12.75" customHeight="1" s="69">
       <c r="A62" s="4">
-        <f>'GPT-5 Generation'!A62</f>
+        <f>'GPT-5.5 Grading'!A62</f>
         <v/>
       </c>
       <c r="B62" s="4">
-        <f>'GPT-5 Generation'!B62</f>
+        <f>'GPT-5.5 Grading'!B62</f>
         <v/>
       </c>
       <c r="C62" s="5" t="n"/>
@@ -2142,11 +2142,11 @@
     </row>
     <row r="63" ht="12.75" customHeight="1" s="69">
       <c r="A63" s="4">
-        <f>'GPT-5 Generation'!A63</f>
+        <f>'GPT-5.5 Grading'!A63</f>
         <v/>
       </c>
       <c r="B63" s="4">
-        <f>'GPT-5 Generation'!B63</f>
+        <f>'GPT-5.5 Grading'!B63</f>
         <v/>
       </c>
       <c r="C63" s="5" t="n"/>
@@ -2154,11 +2154,11 @@
     </row>
     <row r="64" ht="12.75" customHeight="1" s="69">
       <c r="A64" s="4">
-        <f>'GPT-5 Generation'!A64</f>
+        <f>'GPT-5.5 Grading'!A64</f>
         <v/>
       </c>
       <c r="B64" s="4">
-        <f>'GPT-5 Generation'!B64</f>
+        <f>'GPT-5.5 Grading'!B64</f>
         <v/>
       </c>
       <c r="C64" s="5" t="n"/>
@@ -2166,11 +2166,11 @@
     </row>
     <row r="65" ht="12.75" customHeight="1" s="69">
       <c r="A65" s="4">
-        <f>'GPT-5 Generation'!A65</f>
+        <f>'GPT-5.5 Grading'!A65</f>
         <v/>
       </c>
       <c r="B65" s="4">
-        <f>'GPT-5 Generation'!B65</f>
+        <f>'GPT-5.5 Grading'!B65</f>
         <v/>
       </c>
       <c r="C65" s="5" t="n"/>
@@ -2178,11 +2178,11 @@
     </row>
     <row r="66" ht="12.75" customHeight="1" s="69">
       <c r="A66" s="4">
-        <f>'GPT-5 Generation'!A66</f>
+        <f>'GPT-5.5 Grading'!A66</f>
         <v/>
       </c>
       <c r="B66" s="4">
-        <f>'GPT-5 Generation'!B66</f>
+        <f>'GPT-5.5 Grading'!B66</f>
         <v/>
       </c>
       <c r="C66" s="5" t="n"/>
@@ -2190,11 +2190,11 @@
     </row>
     <row r="67" ht="12.75" customHeight="1" s="69">
       <c r="A67" s="4">
-        <f>'GPT-5 Generation'!A67</f>
+        <f>'GPT-5.5 Grading'!A67</f>
         <v/>
       </c>
       <c r="B67" s="4">
-        <f>'GPT-5 Generation'!B67</f>
+        <f>'GPT-5.5 Grading'!B67</f>
         <v/>
       </c>
       <c r="C67" s="5" t="n"/>
@@ -2202,111 +2202,111 @@
     </row>
     <row r="68" ht="12.75" customHeight="1" s="69">
       <c r="A68" s="4">
-        <f>'GPT-5 Generation'!A68</f>
+        <f>'GPT-5.5 Grading'!A68</f>
         <v/>
       </c>
       <c r="B68" s="4">
-        <f>'GPT-5 Generation'!B68</f>
+        <f>'GPT-5.5 Grading'!B68</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1" s="69">
       <c r="A69" s="4">
-        <f>'GPT-5 Generation'!A69</f>
+        <f>'GPT-5.5 Grading'!A69</f>
         <v/>
       </c>
       <c r="B69" s="4">
-        <f>'GPT-5 Generation'!B69</f>
+        <f>'GPT-5.5 Grading'!B69</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1" s="69">
       <c r="A70" s="4">
-        <f>'GPT-5 Generation'!A70</f>
+        <f>'GPT-5.5 Grading'!A70</f>
         <v/>
       </c>
       <c r="B70" s="4">
-        <f>'GPT-5 Generation'!B70</f>
+        <f>'GPT-5.5 Grading'!B70</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1" s="69">
       <c r="A71" s="6">
-        <f>'GPT-5 Generation'!A71</f>
+        <f>'GPT-5.5 Grading'!A71</f>
         <v/>
       </c>
       <c r="B71" s="6">
-        <f>'GPT-5 Generation'!B71</f>
+        <f>'GPT-5.5 Grading'!B71</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1" s="69">
       <c r="A72" s="7">
-        <f>'GPT-5 Generation'!A72</f>
+        <f>'GPT-5.5 Grading'!A72</f>
         <v/>
       </c>
       <c r="B72" s="7">
-        <f>'GPT-5 Generation'!B72</f>
+        <f>'GPT-5.5 Grading'!B72</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1" s="69">
       <c r="A73" s="4">
-        <f>'GPT-5 Generation'!A73</f>
+        <f>'GPT-5.5 Grading'!A73</f>
         <v/>
       </c>
       <c r="B73" s="4">
-        <f>'GPT-5 Generation'!B73</f>
+        <f>'GPT-5.5 Grading'!B73</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1" s="69">
       <c r="A74" s="4">
-        <f>'GPT-5 Generation'!A74</f>
+        <f>'GPT-5.5 Grading'!A74</f>
         <v/>
       </c>
       <c r="B74" s="4">
-        <f>'GPT-5 Generation'!B74</f>
+        <f>'GPT-5.5 Grading'!B74</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1" s="69">
       <c r="A75" s="4">
-        <f>'GPT-5 Generation'!A75</f>
+        <f>'GPT-5.5 Grading'!A75</f>
         <v/>
       </c>
       <c r="B75" s="4">
-        <f>'GPT-5 Generation'!B75</f>
+        <f>'GPT-5.5 Grading'!B75</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1" s="69">
       <c r="A76" s="4">
-        <f>'GPT-5 Generation'!A76</f>
+        <f>'GPT-5.5 Grading'!A76</f>
         <v/>
       </c>
       <c r="B76" s="4">
-        <f>'GPT-5 Generation'!B76</f>
+        <f>'GPT-5.5 Grading'!B76</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1" s="69">
       <c r="A77" s="4">
-        <f>'GPT-5 Generation'!A77</f>
+        <f>'GPT-5.5 Grading'!A77</f>
         <v/>
       </c>
       <c r="B77" s="4">
-        <f>'GPT-5 Generation'!B77</f>
+        <f>'GPT-5.5 Grading'!B77</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1" s="69">
       <c r="A78" s="4">
-        <f>'GPT-5 Generation'!A78</f>
+        <f>'GPT-5.5 Grading'!A78</f>
         <v/>
       </c>
       <c r="B78" s="4">
-        <f>'GPT-5 Generation'!B78</f>
+        <f>'GPT-5.5 Grading'!B78</f>
         <v/>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>Grading</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
@@ -6055,11 +6055,11 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>Student model starts with Inactive state instead of Scheduled; initial state points to Inactive not Scheduled.</t>
+          <t>Initial pseudostate goes to Scheduled.</t>
         </is>
       </c>
     </row>
@@ -6075,11 +6075,11 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>No Scheduled state exists in student submission; uses Inactive state which does not represent the scheduled waiting period.</t>
+          <t>Scheduled state is explicitly modeled.</t>
         </is>
       </c>
     </row>
@@ -6095,11 +6095,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Transition exists from Inactive to Active with scheduledStopBegins event but does not match the expected atBeginningStopDuration semantics exactly.</t>
+          <t>Scheduled enters Active at the start of the stop duration.</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Actions pOn() and setCS(firstSegment) are present on the Inactive to Active transition.</t>
+          <t>Transition powers on and sets the first segment.</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Active composite state is present and contains the required regions.</t>
+          <t>Active composite state contains the train behavior.</t>
         </is>
       </c>
     </row>
@@ -6155,11 +6155,11 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Student has Operation region which serves similar purpose but is named differently; contains Journey and EmergencyStopped states.</t>
+          <t>ControlRegion represents the train control behavior.</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Journey composite state in student submission represents the train movement logic equivalent to TrainMovement.</t>
+          <t>Control composite contains the normal movement and stopping states.</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Initial state in Journey points to InitialStationStop which represents the station stop behavior.</t>
+          <t>Control initially enters AtStation.</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>InitialStationStop and DwellingAtStation states together represent AtStation behavior; doors open and close appropriately.</t>
+          <t>AtStation is explicitly modeled.</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>openDoors() action is present when entering DwellingAtStation after stoppedDetected.</t>
+          <t>AtStation has an entry note to open doors.</t>
         </is>
       </c>
     </row>
@@ -6255,11 +6255,11 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>closeDoors() action is present when leaving DwellingAtStation and InitialStationStop states.</t>
+          <t>Doors close only on the nonfinal departure transition and not as a general exit behavior.</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Transition from InitialStationStop and DwellingAtStation to Running after stopDuration with setSpeed action.</t>
+          <t>Nonfinal station departure after stopDuration goes to Moving which is the normal running state.</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Student uses separate states for final station vs intermediate stations; StoppingAtStation handles non-final stations.</t>
+          <t>The nonfinal departure uses a !finalStation guard.</t>
         </is>
       </c>
     </row>
@@ -6315,11 +6315,11 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Transition from FinalStationDwelling to Inactive after stopDuration exists but goes to Inactive rather than separate Arrived state.</t>
+          <t>Final station departure after stopDuration goes to Off which represents powered off arrival.</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Guard finalStation() is used to distinguish final station in transition from Running to StoppingAtFinalStation.</t>
+          <t>The final station transition is guarded by finalStation.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>pOff() action is present on transition from FinalStationDwelling to Inactive.</t>
+          <t>The final station transition performs pOff.</t>
         </is>
       </c>
       <c r="E17" s="5" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Running state represents the normal running behavior equivalent to StopNotRequired.</t>
+          <t>Moving represents the state where no stop is currently required.</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>setSpeed action is present on transitions entering Running state from various sources.</t>
+          <t>Required speed is set when entering or remaining in the normal moving behavior.</t>
         </is>
       </c>
     </row>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Self-transition on Running with segmentUpdated event and guard for regular segment type with setSpeed action.</t>
+          <t>Moving self transition handles a new regular segment.</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Guard currentSegment.type==regular checks for regular segment type.</t>
+          <t>Regular segment is included in the self transition guard.</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Transition from Running to StoppingAtRedLight when segmentUpdated with trafficLight type and lightRed() guard.</t>
+          <t>New red traffic light segment leads to StoppingAtLight.</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Guard currentSegment.type==trafficLight &amp;&amp; lightRed() correctly checks for red traffic light.</t>
+          <t>Traffic light and red conditions are both present.</t>
         </is>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Self-transition on Running for traffic light segment when not red with setSpeed action.</t>
+          <t>Green traffic light segment remains in Moving.</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Guard currentSegment.type==trafficLight &amp;&amp; !lightRed() correctly checks for green traffic light.</t>
+          <t>Traffic light and green condition are represented.</t>
         </is>
       </c>
     </row>
@@ -6571,11 +6571,11 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Transition from Running to StoppingAtStation when station segment and stationOnItinerary() and not final station.</t>
+          <t>Station segments lead to StoppingAtStation but the need to stop is not checked.</t>
         </is>
       </c>
     </row>
@@ -6591,11 +6591,11 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Guard currentSegment.type==station &amp;&amp; stationOnItinerary() checks if stop is required at station.</t>
+          <t>The guard checks station segment only and omits stopRequired.</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>StoppingAtRedLight state represents the approaching red light behavior.</t>
+          <t>StoppingAtLight represents approaching a red light stop.</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>stopAL action is present on transition to StoppingAtRedLight state.</t>
+          <t>stopAL is executed when the red light stop is initiated.</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Transition from StoppingAtRedLight to WaitingAtRedLight on stoppedDetected event.</t>
+          <t>Stopped event moves to WaitingAtLight.</t>
         </is>
       </c>
       <c r="E30" s="5" t="n"/>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>WaitingAtRedLight state represents waiting at red traffic light.</t>
+          <t>WaitingAtLight represents the train waiting at the red light.</t>
         </is>
       </c>
       <c r="E31" s="5" t="n"/>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Transition from WaitingAtRedLight to Running on lightGreen event with setSpeed action.</t>
+          <t>Green event returns to Moving and sets speed.</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>StoppingAtStation state represents approaching station behavior.</t>
+          <t>StoppingAtStation represents approaching a station stop.</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>stopAL action is present on transition to StoppingAtStation state.</t>
+          <t>stopAL is executed when the station stop is initiated.</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Transition from StoppingAtStation to DwellingAtStation on stoppedDetected event with openDoors action.</t>
+          <t>Stopped event moves from StoppingAtStation to AtStation.</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>History state H is present in Journey composite state for resuming after emergency.</t>
+          <t>H is modeled and used to resume from Emergency.</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>EmergencyStopped state represents emergency stop behavior.</t>
+          <t>Emergency state is explicitly modeled.</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Transition from Journey to EmergencyStopped on obstructionDetected event with eStop action.</t>
+          <t>Control transitions to Emergency on obstruction which represents the emergency trigger.</t>
         </is>
       </c>
       <c r="E38" s="5" t="n"/>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>eStop() action is present on transition to EmergencyStopped state.</t>
+          <t>Emergency transition performs eStop.</t>
         </is>
       </c>
       <c r="E39" s="5" t="n"/>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Transition from EmergencyStopped to history state H on obstructionCleared event.</t>
+          <t>Cleared transition returns from Emergency to H.</t>
         </is>
       </c>
       <c r="E40" s="5" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>SegmentDetection region represents the SDS functionality.</t>
+          <t>SDSRegion is modeled as an independent region.</t>
         </is>
       </c>
       <c r="E41" s="5" t="n"/>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Initial state in SegmentDetection region points to MonitoringSegment.</t>
+          <t>SDSRegion initially enters SDS_Running.</t>
         </is>
       </c>
       <c r="E42" s="5" t="n"/>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>MonitoringSegment state represents the active segment detection behavior.</t>
+          <t>SDS_Running represents the active SDS.</t>
         </is>
       </c>
       <c r="E43" s="5" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Self-transition on MonitoringSegment with after(1s) trigger and guard for segment change.</t>
+          <t>SDS checks every second with a self transition.</t>
         </is>
       </c>
       <c r="E44" s="5" t="n"/>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Guard enteredNewSegment(segment) checks if segment has changed.</t>
+          <t>The SDS transition is guarded by newSegmentDetected.</t>
         </is>
       </c>
       <c r="E45" s="5" t="n"/>
@@ -7151,11 +7151,11 @@
         </is>
       </c>
       <c r="C46" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Actions setCS(segment) and raiseSegmentUpdated() are present; raiseSegmentUpdated serves as enteringSegment event.</t>
+          <t>setCS is present but no enteringSegment event or action is generated.</t>
         </is>
       </c>
       <c r="E46" s="5" t="n"/>
@@ -7189,11 +7189,11 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Self-transition on MonitoringSegment with after(1s) trigger when no segment change detected.</t>
+          <t>No explicit no segment change transition is modeled.</t>
         </is>
       </c>
       <c r="E47" s="5" t="n"/>
@@ -7227,11 +7227,11 @@
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Guard !enteredNewSegment(segment) checks if segment has not changed.</t>
+          <t>No negated segment change guard is modeled.</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>MovementDetection region represents the MDS functionality.</t>
+          <t>MDSRegion is modeled as an independent region.</t>
         </is>
       </c>
     </row>
@@ -7267,11 +7267,11 @@
         </is>
       </c>
       <c r="C50" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Initial state in MovementDetection region points to Stopped.</t>
+          <t>MDS initializes to a generic running state rather than Stopped.</t>
         </is>
       </c>
     </row>
@@ -7287,11 +7287,11 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Stopped state is present in MovementDetection region.</t>
+          <t>No Stopped state is modeled in MDS.</t>
         </is>
       </c>
     </row>
@@ -7307,11 +7307,11 @@
         </is>
       </c>
       <c r="C52" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Transition from Stopped to Moving with after(1s) trigger and trainMoving() guard.</t>
+          <t>No MDS transition from Stopped to Moving is modeled.</t>
         </is>
       </c>
     </row>
@@ -7327,11 +7327,11 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Guard trainMoving() represents speed &gt; 0 condition.</t>
+          <t>No speed greater than zero guard is modeled in MDS.</t>
         </is>
       </c>
     </row>
@@ -7347,11 +7347,11 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Self-transition on Stopped with after(1s) trigger when not moving.</t>
+          <t>No MDS self transition for remaining stopped is modeled.</t>
         </is>
       </c>
     </row>
@@ -7367,11 +7367,11 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Guard !trainMoving() represents speed == 0 condition.</t>
+          <t>No speed equals zero guard is modeled for stopped detection.</t>
         </is>
       </c>
     </row>
@@ -7387,11 +7387,11 @@
         </is>
       </c>
       <c r="C56" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>Student raises stoppedDetected event on Moving to Stopped transition but not on Stopped self-loop; partial coverage.</t>
+          <t>MDS does not emit a stopped action or event.</t>
         </is>
       </c>
     </row>
@@ -7407,11 +7407,11 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Moving state is present in MovementDetection region.</t>
+          <t>Moving exists in control but not as an MDS detection state.</t>
         </is>
       </c>
     </row>
@@ -7427,11 +7427,11 @@
         </is>
       </c>
       <c r="C58" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>Transition from Moving to Stopped with after(1s) trigger and raiseStoppedDetected action.</t>
+          <t>No MDS transition from Moving to Stopped is modeled.</t>
         </is>
       </c>
     </row>
@@ -7447,11 +7447,11 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Guard !trainMoving() represents speed == 0 condition.</t>
+          <t>No speed equals zero guard is modeled for Moving to Stopped.</t>
         </is>
       </c>
     </row>
@@ -7467,11 +7467,11 @@
         </is>
       </c>
       <c r="C60" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>raiseStoppedDetected() action is present on Moving to Stopped transition.</t>
+          <t>MDS does not generate stopped when speed becomes zero.</t>
         </is>
       </c>
     </row>
@@ -7487,11 +7487,11 @@
         </is>
       </c>
       <c r="C61" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>Self-transition on Moving with after(1s) trigger when still moving.</t>
+          <t>No MDS self transition for remaining moving is modeled.</t>
         </is>
       </c>
     </row>
@@ -7507,11 +7507,11 @@
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Guard trainMoving() represents speed &gt; 0 condition.</t>
+          <t>No speed greater than zero guard is modeled for remaining moving.</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>ObstructionDetection region represents the ODS functionality.</t>
+          <t>ODSRegion is modeled as an independent region.</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>Initial state in ObstructionDetection region points to TracksClear.</t>
+          <t>ODSRegion initially enters ODS_Running.</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>TracksClear and TracksObstructed states together represent the ODS active monitoring behavior.</t>
+          <t>ODS_Running represents active obstruction detection.</t>
         </is>
       </c>
     </row>
@@ -7587,11 +7587,11 @@
         </is>
       </c>
       <c r="C66" s="18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>Transition from TracksClear to TracksObstructed with after(1s) trigger and tracksObstructed() guard with raiseObstructionDetected action.</t>
+          <t>ODS checks every second but the obstacle case is not explicitly separated.</t>
         </is>
       </c>
     </row>
@@ -7607,11 +7607,11 @@
         </is>
       </c>
       <c r="C67" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>Guard tracksObstructed() checks for obstacle detection.</t>
+          <t>No obstacleDetected guard is shown.</t>
         </is>
       </c>
     </row>
@@ -7627,11 +7627,11 @@
         </is>
       </c>
       <c r="C68" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>raiseObstructionDetected() action triggers emergency transition in Operation region.</t>
+          <t>ODS does not generate an emergency event.</t>
         </is>
       </c>
     </row>
@@ -7647,11 +7647,11 @@
         </is>
       </c>
       <c r="C69" s="18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t>Self-transitions on TracksClear and TracksObstructed when conditions remain unchanged.</t>
+          <t>The unguarded periodic check can cover normal checking but lacks the no obstacle case.</t>
         </is>
       </c>
     </row>
@@ -7667,11 +7667,11 @@
         </is>
       </c>
       <c r="C70" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" s="19" t="inlineStr">
         <is>
-          <t>Guard !tracksObstructed() checks for no obstacle.</t>
+          <t>No negated obstacle guard is shown.</t>
         </is>
       </c>
     </row>
@@ -7687,11 +7687,11 @@
         </is>
       </c>
       <c r="C71" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t>No separate Arrived state; train goes directly to Inactive after final station dwelling.</t>
+          <t>Off state represents the final powered off arrival condition.</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D72" s="21" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional states present.</t>
+          <t>No fundamentally incorrect extra states are present.</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional transitions present.</t>
+          <t>No fundamentally incorrect extra transitions are present.</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional guards present.</t>
+          <t>No fundamentally incorrect extra guards are present.</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional actions present.</t>
+          <t>Extra checking actions are reasonable internal abstractions.</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional composite states present.</t>
+          <t>No fundamentally incorrect extra composite states are present.</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional regions present.</t>
+          <t>No fundamentally incorrect extra regions are present.</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional history states present.</t>
+          <t>No fundamentally incorrect extra history states are present.</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
     <row r="1" ht="15.75" customHeight="1" s="69">
       <c r="A1" s="70" t="inlineStr">
         <is>
-          <t>Generated by GPT-5</t>
+          <t>Generated by Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="J1" s="22" t="inlineStr">
@@ -12588,15 +12588,15 @@
         <v/>
       </c>
       <c r="C3" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$71, $A3, 'GPT-5 Generation'!$C$2:$C$71)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$71, $A3, 'GPT-5.5 Grading'!$C$2:$C$71)</f>
         <v/>
       </c>
       <c r="D3" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$72:$A$78, $A3, 'GPT-5 Generation'!$C$72:$C$78)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$72:$A$78, $A3, 'GPT-5.5 Grading'!$C$72:$C$78)</f>
         <v/>
       </c>
       <c r="E3" s="26">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$71, $A3, 'GPT-5 Generation'!$C$2:$C$71,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$71, $A3, 'GPT-5.5 Grading'!$C$2:$C$71,0)</f>
         <v/>
       </c>
       <c r="F3" s="26">
@@ -12624,15 +12624,15 @@
         <v/>
       </c>
       <c r="C4" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$71, $A4, 'GPT-5 Generation'!$C$2:$C$71)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$71, $A4, 'GPT-5.5 Grading'!$C$2:$C$71)</f>
         <v/>
       </c>
       <c r="D4" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$72:$A$78, $A4, 'GPT-5 Generation'!$C$72:$C$78)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$72:$A$78, $A4, 'GPT-5.5 Grading'!$C$72:$C$78)</f>
         <v/>
       </c>
       <c r="E4" s="26">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$71, $A4, 'GPT-5 Generation'!$C$2:$C$71,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$71, $A4, 'GPT-5.5 Grading'!$C$2:$C$71,0)</f>
         <v/>
       </c>
       <c r="F4" s="26">
@@ -12664,15 +12664,15 @@
         <v/>
       </c>
       <c r="C5" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$71, $A5, 'GPT-5 Generation'!$C$2:$C$71)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$71, $A5, 'GPT-5.5 Grading'!$C$2:$C$71)</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$72:$A$78, $A5, 'GPT-5 Generation'!$C$72:$C$78)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$72:$A$78, $A5, 'GPT-5.5 Grading'!$C$72:$C$78)</f>
         <v/>
       </c>
       <c r="E5" s="26">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$71, $A5, 'GPT-5 Generation'!$C$2:$C$71,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$71, $A5, 'GPT-5.5 Grading'!$C$2:$C$71,0)</f>
         <v/>
       </c>
       <c r="F5" s="26">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="J5" s="24" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
     </row>
@@ -12704,15 +12704,15 @@
         <v/>
       </c>
       <c r="C6" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$71, $A6, 'GPT-5 Generation'!$C$2:$C$71)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$71, $A6, 'GPT-5.5 Grading'!$C$2:$C$71)</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$72:$A$78, $A6, 'GPT-5 Generation'!$C$72:$C$78)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$72:$A$78, $A6, 'GPT-5.5 Grading'!$C$72:$C$78)</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$71, $A6, 'GPT-5 Generation'!$C$2:$C$71,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$71, $A6, 'GPT-5.5 Grading'!$C$2:$C$71,0)</f>
         <v/>
       </c>
       <c r="F6" s="26">
@@ -12739,15 +12739,15 @@
         <v/>
       </c>
       <c r="C7" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$71, $A7, 'GPT-5 Generation'!$C$2:$C$71)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$71, $A7, 'GPT-5.5 Grading'!$C$2:$C$71)</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$72:$A$78, $A7, 'GPT-5 Generation'!$C$72:$C$78)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$72:$A$78, $A7, 'GPT-5.5 Grading'!$C$72:$C$78)</f>
         <v/>
       </c>
       <c r="E7" s="26">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$71, $A7, 'GPT-5 Generation'!$C$2:$C$71,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$71, $A7, 'GPT-5.5 Grading'!$C$2:$C$71,0)</f>
         <v/>
       </c>
       <c r="F7" s="26">
@@ -12779,15 +12779,15 @@
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$71, $A8, 'GPT-5 Generation'!$C$2:$C$71)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$71, $A8, 'GPT-5.5 Grading'!$C$2:$C$71)</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$72:$A$78, $A8, 'GPT-5 Generation'!$C$72:$C$78)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$72:$A$78, $A8, 'GPT-5.5 Grading'!$C$72:$C$78)</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$71, $A8, 'GPT-5 Generation'!$C$2:$C$71,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$71, $A8, 'GPT-5.5 Grading'!$C$2:$C$71,0)</f>
         <v/>
       </c>
       <c r="F8" s="26">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="J8" s="73" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -12819,15 +12819,15 @@
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$71, $A9, 'GPT-5 Generation'!$C$2:$C$71)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$71, $A9, 'GPT-5.5 Grading'!$C$2:$C$71)</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>SUMIF('GPT-5 Generation'!$A$72:$A$78, $A9, 'GPT-5 Generation'!$C$72:$C$78)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$72:$A$78, $A9, 'GPT-5.5 Grading'!$C$72:$C$78)</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$71, $A9, 'GPT-5 Generation'!$C$2:$C$71,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$71, $A9, 'GPT-5.5 Grading'!$C$2:$C$71,0)</f>
         <v/>
       </c>
       <c r="F9" s="26">
